--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Data Insights Enterprise\Sporstats\Telegram Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7170FCE5-5D45-47D9-A26F-0134F8AE2714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E98BDCA-C3DF-42FB-8E58-D105F850AD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{3F6758F4-AD12-46A6-80C3-A28786E12809}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{3F6758F4-AD12-46A6-80C3-A28786E12809}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="136">
   <si>
     <t>Partido</t>
   </si>
@@ -194,9 +194,6 @@
     <t>ML (Prob)</t>
   </si>
   <si>
-    <t>🔵🔵🔵</t>
-  </si>
-  <si>
     <t>SoT +8.5 (66%)</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>Tarjetas +4.5 (66%)</t>
   </si>
   <si>
-    <t>🔵🔵</t>
-  </si>
-  <si>
     <t>Uruguay – Primera División</t>
   </si>
   <si>
@@ -230,24 +224,15 @@
     <t>Juventud o Empate (61%)</t>
   </si>
   <si>
-    <t>Goles -2.5 (69%)</t>
-  </si>
-  <si>
     <t>Corners -9.5 (61%)</t>
   </si>
   <si>
     <t>Tarjetas +4.5 (71%)</t>
   </si>
   <si>
-    <t>Defensor Sporting vs Albion</t>
-  </si>
-  <si>
     <t>Defensor o Empate (64%)</t>
   </si>
   <si>
-    <t>Goles -2.5 (67%)</t>
-  </si>
-  <si>
     <t>SoT -8.5 (63%)</t>
   </si>
   <si>
@@ -263,9 +248,6 @@
     <t>Huracán Gana (76%)</t>
   </si>
   <si>
-    <t>Goles +1.5 (72%)</t>
-  </si>
-  <si>
     <t>La Equidad vs Junior</t>
   </si>
   <si>
@@ -278,24 +260,9 @@
     <t>Peñarol o Empate (74%)</t>
   </si>
   <si>
-    <t>Goles +1.5 (71%)</t>
-  </si>
-  <si>
-    <t>Brasil – Serie A</t>
-  </si>
-  <si>
-    <t>Athletico Paranaense vs Botafogo RJ</t>
-  </si>
-  <si>
-    <t>Goles -2.5 (68%)</t>
-  </si>
-  <si>
     <t>Newell’s Gana (72%)</t>
   </si>
   <si>
-    <t>Goles +1.5 (69%)</t>
-  </si>
-  <si>
     <t>Corners +8.5 (63%)</t>
   </si>
   <si>
@@ -308,104 +275,15 @@
     <t>Corners -9.5 (62%)</t>
   </si>
   <si>
-    <t>Llaneros vs Once Caldas</t>
-  </si>
-  <si>
     <t>SoT -8.5 (60%)</t>
   </si>
   <si>
-    <t>Tabla 2 – Ultrafiltrada</t>
-  </si>
-  <si>
     <t>Newell’s vs Acassuso</t>
   </si>
   <si>
     <t>Pasto vs Atlético Nacional</t>
   </si>
   <si>
-    <t>Tabla 3 – Stakes sugeridos</t>
-  </si>
-  <si>
-    <t>Tabla 4 – Combinadas de baja varianza</t>
-  </si>
-  <si>
-    <t>Prob. combinada</t>
-  </si>
-  <si>
-    <t>03:00 p. m. / 05:15 p. m.</t>
-  </si>
-  <si>
-    <t>Huracán Gana + Newell’s Gana</t>
-  </si>
-  <si>
-    <t>04:25 p. m. / 05:20 p. m.</t>
-  </si>
-  <si>
-    <t>Uruguay + Colombia</t>
-  </si>
-  <si>
-    <t>Peñarol o Empate + Nacional o Empate</t>
-  </si>
-  <si>
-    <t>03:10 p. m. / 07:30 p. m.</t>
-  </si>
-  <si>
-    <t>La Equidad vs Junior Goles -2.5 + Llaneros vs Once Caldas Goles -2.5</t>
-  </si>
-  <si>
-    <t>Tabla 5 – Goles probables</t>
-  </si>
-  <si>
-    <t>Pick de goles</t>
-  </si>
-  <si>
-    <t>Tabla 6 – Top valor estadístico</t>
-  </si>
-  <si>
-    <t>Lectura rápida ProHeat</t>
-  </si>
-  <si>
-    <t>Lectura</t>
-  </si>
-  <si>
-    <t>Favorito claro de copa; mejor en ML que en corners</t>
-  </si>
-  <si>
-    <t>Pick fuerte por localía y jerarquía, pero no forzar overs altos</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Partido de fricción; el valor está más en </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>under</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que en ganador</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Duelo más cerrado por bajas y volatilidad; preferible mercado conservador </t>
-  </si>
-  <si>
-    <t>Copa con favorito superior; mejor ML y over corto que líneas altas de corners</t>
-  </si>
-  <si>
     <t>Goles Local</t>
   </si>
   <si>
@@ -572,90 +450,6 @@
   </si>
   <si>
     <t>SoT +9.5 (68%)</t>
-  </si>
-  <si>
-    <t>🔥 TABLA 2 – ULTRAFILTRADA</t>
-  </si>
-  <si>
-    <t>Unión vs Agropecuario</t>
-  </si>
-  <si>
-    <t>Kenia vs Granada</t>
-  </si>
-  <si>
-    <t>💰 TABLA 3 – STAKES</t>
-  </si>
-  <si>
-    <t>Millonarios ML</t>
-  </si>
-  <si>
-    <t>🔵🔵🔵🔵</t>
-  </si>
-  <si>
-    <t>Unión ML</t>
-  </si>
-  <si>
-    <t>Kenia ML</t>
-  </si>
-  <si>
-    <t>Chile vs NZ</t>
-  </si>
-  <si>
-    <t>Chile o Empate</t>
-  </si>
-  <si>
-    <t>🔗 TABLA 4 – COMBINADAS</t>
-  </si>
-  <si>
-    <t>Probabilidad</t>
-  </si>
-  <si>
-    <t>06:15 + 07:20</t>
-  </si>
-  <si>
-    <t>Copa + Colombia</t>
-  </si>
-  <si>
-    <t>Unión gana + Millonarios gana</t>
-  </si>
-  <si>
-    <t>08:00 + 12:00</t>
-  </si>
-  <si>
-    <t>Kenia gana + Chile o Empate</t>
-  </si>
-  <si>
-    <t>04:00 + 05:55</t>
-  </si>
-  <si>
-    <t>Defensor o Empate + Maldonado o Empate</t>
-  </si>
-  <si>
-    <t>⚽ TABLA 5 – GOLES PROBABLES</t>
-  </si>
-  <si>
-    <t>Goles +1.5 (70%)</t>
-  </si>
-  <si>
-    <t>Trinidad vs Gabón</t>
-  </si>
-  <si>
-    <t>Goles +1.5 (68%)</t>
-  </si>
-  <si>
-    <t>Medellín vs América</t>
-  </si>
-  <si>
-    <t>📈 TABLA 6 – TOP VALOR ESTADÍSTICO</t>
-  </si>
-  <si>
-    <t>Millonarios gana (76%)</t>
-  </si>
-  <si>
-    <t>Unión gana (74%)</t>
-  </si>
-  <si>
-    <t>Kenia gana (74%)</t>
   </si>
 </sst>
 </file>
@@ -1137,10 +931,10 @@
         <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1157,28 +951,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1186,28 +980,28 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1215,28 +1009,28 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1244,28 +1038,28 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1273,28 +1067,28 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1302,28 +1096,28 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1331,28 +1125,28 @@
         <v>0.375</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1360,28 +1154,28 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1392,25 +1186,25 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1421,25 +1215,25 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1450,25 +1244,25 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1479,25 +1273,25 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1508,25 +1302,25 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1534,28 +1328,28 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
@@ -1566,430 +1360,202 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>169</v>
-      </c>
+      <c r="A19" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="A22" s="12"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="A23" s="12"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="A24" s="12"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="A25" s="12"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="A26" s="12"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="29" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="A29" s="3"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="12"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A33" s="12"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A34" s="12"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
-        <v>0</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="A35" s="12"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
     </row>
     <row r="38" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="A38" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="6">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="6">
-        <v>0.52</v>
-      </c>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="46" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="A46" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
-        <v>0</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>189</v>
-      </c>
+      <c r="A49" s="12"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>191</v>
-      </c>
+      <c r="A50" s="12"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A51" s="12"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <v>0.71527777777777779</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="A52" s="12"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="A53" s="12"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
     </row>
     <row r="56" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="A56" s="3"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>194</v>
-      </c>
+      <c r="A59" s="12"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="A60" s="12"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>196</v>
-      </c>
+      <c r="A61" s="12"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
-        <v>0</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="A62" s="12"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1999,620 +1565,345 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E4A882-59B8-48F6-BBA6-4830D71F0398}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>90</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2"/>
+    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="12">
+        <v>0.625</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="12">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
-        <v>0.625</v>
+        <v>0.71875</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
-        <v>0.68402777777777779</v>
+        <v>0.63194444444444442</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
-        <v>0.71875</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>93</v>
-      </c>
+    </row>
+    <row r="8" spans="1:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="12"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
-        <v>0.625</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
-        <v>0.71875</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="12">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
-        <v>0.625</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
-        <v>0.6875</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
-        <v>0.71875</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
-        <v>0.8125</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="A12" s="12"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="12"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="24" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="12"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="12"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="12"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="12"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="12"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="12"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="12"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="12"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="12"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="37" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="12"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
-        <v>0.625</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
-        <v>0.71875</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="13" t="s">
-        <v>106</v>
-      </c>
+      <c r="A41" s="12"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="12"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="12"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="12"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="46" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="13"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="12"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <v>0.625</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
-        <v>0.6875</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="116" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
-        <v>0.71875</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-    </row>
-    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A73" s="11"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="12"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="12"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="12"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="12"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="62" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+    </row>
+    <row r="71" spans="1:1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A71" s="11"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="8"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="8"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="4"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
@@ -2661,18 +1952,6 @@
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="4"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="4"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
